--- a/domain/demo_corpus/files/crm_data_dictionary.xlsx
+++ b/domain/demo_corpus/files/crm_data_dictionary.xlsx
@@ -536,7 +536,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -569,7 +568,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -602,7 +600,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -635,7 +632,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -668,7 +664,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -701,7 +696,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -734,7 +728,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
